--- a/data/ams_weekly_data/Audio_Array/ads_report_week18.xlsx
+++ b/data/ams_weekly_data/Audio_Array/ads_report_week18.xlsx
@@ -11767,7 +11767,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I42"/>
+  <dimension ref="A1:I46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11929,19 +11929,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>46500</v>
+        <v>25648</v>
       </c>
       <c r="E5" t="n">
-        <v>272</v>
+        <v>150</v>
       </c>
       <c r="F5" t="n">
-        <v>4750.01</v>
+        <v>2619.947705339994</v>
       </c>
       <c r="G5" t="n">
-        <v>24960.17</v>
+        <v>13767.20051460863</v>
       </c>
       <c r="H5" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -11953,28 +11953,28 @@
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Audio Array-B0BLJVJ2GN-AA 05 Suspension-SB-PT</t>
+          <t>Audio Array-B0B4DPX2J2-Condenser AM C1-SBV-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>B0B4G8PH2P</t>
+          <t>B0D3M1B4Z8</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>15630.33333333333</v>
+        <v>8228</v>
       </c>
       <c r="E6" t="n">
-        <v>105</v>
+        <v>48</v>
       </c>
       <c r="F6" t="n">
-        <v>976.4433333333333</v>
+        <v>840.5121949945976</v>
       </c>
       <c r="G6" t="n">
-        <v>4354.513333333333</v>
+        <v>4416.691180468736</v>
       </c>
       <c r="H6" t="n">
-        <v>4.333333333333333</v>
+        <v>2</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -11986,28 +11986,28 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Audio Array-B0BLJVJ2GN-AA 05 Suspension-SB-PT</t>
+          <t>Audio Array-B0B4DPX2J2-Condenser AM C1-SBV-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>B0BLJVJ2GN</t>
+          <t>B0FJ2K95XT</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>15630.33333333333</v>
+        <v>12624</v>
       </c>
       <c r="E7" t="n">
-        <v>105</v>
+        <v>74</v>
       </c>
       <c r="F7" t="n">
-        <v>976.4433333333333</v>
+        <v>1289.550099665409</v>
       </c>
       <c r="G7" t="n">
-        <v>4354.513333333333</v>
+        <v>6776.27830492263</v>
       </c>
       <c r="H7" t="n">
-        <v>4.333333333333333</v>
+        <v>3</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -12024,23 +12024,23 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>B0CF5R3V95</t>
+          <t>B0BLJVJ2GN</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>15630.33333333333</v>
+        <v>22553</v>
       </c>
       <c r="E8" t="n">
-        <v>105</v>
+        <v>152</v>
       </c>
       <c r="F8" t="n">
-        <v>976.4433333333333</v>
+        <v>1408.897288644769</v>
       </c>
       <c r="G8" t="n">
-        <v>4354.513333333333</v>
+        <v>6283.070219504967</v>
       </c>
       <c r="H8" t="n">
-        <v>4.333333333333333</v>
+        <v>6</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -12052,28 +12052,28 @@
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Audio Array-B0BPLZ5CGV-AI 04 Audio Interface-SBV -PT</t>
+          <t>Audio Array-B0BLJVJ2GN-AA 05 Suspension-SB-PT</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>B0BPLZ5CGV</t>
+          <t>B0CF5R3V95</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>86883</v>
+        <v>21386</v>
       </c>
       <c r="E9" t="n">
-        <v>547</v>
+        <v>144</v>
       </c>
       <c r="F9" t="n">
-        <v>4337.17</v>
+        <v>1336.007024835551</v>
       </c>
       <c r="G9" t="n">
-        <v>37535.56</v>
+        <v>5958.011289004725</v>
       </c>
       <c r="H9" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -12085,28 +12085,28 @@
       <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Audio Array-B0CKHVHVQ1-AM W45 Wireless-SBV-KT-Phrase</t>
+          <t>Audio Array-B0BLJVJ2GN-AA 05 Suspension-SB-PT</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>B0CKHVHVQ1</t>
+          <t>B0DT6T6N6B</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>30488</v>
+        <v>2952</v>
       </c>
       <c r="E10" t="n">
-        <v>162</v>
+        <v>20</v>
       </c>
       <c r="F10" t="n">
-        <v>2234.63</v>
+        <v>184.4256865196805</v>
       </c>
       <c r="G10" t="n">
-        <v>21622.9</v>
+        <v>822.458491490309</v>
       </c>
       <c r="H10" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -12118,28 +12118,28 @@
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Audio Array-B0DXFPM4N2-Studio Monitor- SBV-CT</t>
+          <t>Audio Array-B0BPLZ5CGV-AI 04 Audio Interface-SBV -PT</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>B0DXFPM4N2</t>
+          <t>B0BPLZ5CGV</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>17420</v>
+        <v>86883</v>
       </c>
       <c r="E11" t="n">
-        <v>220</v>
+        <v>547</v>
       </c>
       <c r="F11" t="n">
-        <v>1340.92</v>
+        <v>4337.17</v>
       </c>
       <c r="G11" t="n">
-        <v>9635.59</v>
+        <v>37535.56</v>
       </c>
       <c r="H11" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -12151,28 +12151,28 @@
       <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Audio Array-Catch All-Condenser -SB-PT</t>
+          <t>Audio Array-B0CKHVHVQ1-AM W45 Wireless-SBV-KT-Phrase</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>B0B4DPX2J2</t>
+          <t>B0CKHVHVQ1</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>19364</v>
+        <v>30488</v>
       </c>
       <c r="E12" t="n">
-        <v>68.66666666666667</v>
+        <v>162</v>
       </c>
       <c r="F12" t="n">
-        <v>858.6733333333333</v>
+        <v>2234.63</v>
       </c>
       <c r="G12" t="n">
-        <v>1474.86</v>
+        <v>21622.9</v>
       </c>
       <c r="H12" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -12184,28 +12184,28 @@
       <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Audio Array-Catch All-Condenser -SB-PT</t>
+          <t>Audio Array-B0DXFPM4N2-Studio Monitor- SBV-CT</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>B0D3M1B4Z8</t>
+          <t>B0DXFPM4N2</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>19364</v>
+        <v>17420</v>
       </c>
       <c r="E13" t="n">
-        <v>68.66666666666667</v>
+        <v>220</v>
       </c>
       <c r="F13" t="n">
-        <v>858.6733333333333</v>
+        <v>1340.92</v>
       </c>
       <c r="G13" t="n">
-        <v>1474.86</v>
+        <v>9635.59</v>
       </c>
       <c r="H13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -12222,23 +12222,23 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>B0FF9R3GKK</t>
+          <t>B0B4DPX2J2</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>19364</v>
+        <v>31956</v>
       </c>
       <c r="E14" t="n">
-        <v>68.66666666666667</v>
+        <v>113</v>
       </c>
       <c r="F14" t="n">
-        <v>858.6733333333333</v>
+        <v>1417.032820742308</v>
       </c>
       <c r="G14" t="n">
-        <v>1474.86</v>
+        <v>2433.9</v>
       </c>
       <c r="H14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -12250,28 +12250,28 @@
       <c r="A15" t="inlineStr"/>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Audio Array-Multiple Ad Group-SB-PT</t>
+          <t>Audio Array-Catch All-Condenser -SB-PT</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>B0B4DPX2J2</t>
+          <t>B0CH4T2BJD</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13937.28571428571</v>
+        <v>26136</v>
       </c>
       <c r="E15" t="n">
-        <v>58.82142857142857</v>
+        <v>93</v>
       </c>
       <c r="F15" t="n">
-        <v>546.3710714285714</v>
+        <v>1158.987179257692</v>
       </c>
       <c r="G15" t="n">
-        <v>3186.528928571428</v>
+        <v>1990.68</v>
       </c>
       <c r="H15" t="n">
-        <v>1.428571428571429</v>
+        <v>1</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -12288,23 +12288,23 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>B0B4DS678Q</t>
+          <t>B0B4DPX2J2</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13937.28571428571</v>
+        <v>16278</v>
       </c>
       <c r="E16" t="n">
-        <v>58.82142857142857</v>
+        <v>81</v>
       </c>
       <c r="F16" t="n">
-        <v>546.3710714285714</v>
+        <v>1073.331785714286</v>
       </c>
       <c r="G16" t="n">
-        <v>3186.528928571428</v>
+        <v>6383.631785714286</v>
       </c>
       <c r="H16" t="n">
-        <v>1.428571428571429</v>
+        <v>3</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -12321,23 +12321,23 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>B0B4G19R58</t>
+          <t>B0B4DS678Q</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13937.28571428571</v>
+        <v>4589</v>
       </c>
       <c r="E17" t="n">
-        <v>58.82142857142857</v>
+        <v>15</v>
       </c>
       <c r="F17" t="n">
-        <v>546.3710714285714</v>
+        <v>129.1217857142857</v>
       </c>
       <c r="G17" t="n">
-        <v>3186.528928571428</v>
+        <v>114.9817857142857</v>
       </c>
       <c r="H17" t="n">
-        <v>1.428571428571429</v>
+        <v>0</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -12354,23 +12354,23 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>B0B4G1PXWV</t>
+          <t>B0B4G19R58</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13937.28571428571</v>
+        <v>4589</v>
       </c>
       <c r="E18" t="n">
-        <v>58.82142857142857</v>
+        <v>15</v>
       </c>
       <c r="F18" t="n">
-        <v>546.3710714285714</v>
+        <v>129.1217857142857</v>
       </c>
       <c r="G18" t="n">
-        <v>3186.528928571428</v>
+        <v>114.9817857142857</v>
       </c>
       <c r="H18" t="n">
-        <v>1.428571428571429</v>
+        <v>0</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -12387,23 +12387,23 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>B0B4JRQP22</t>
+          <t>B0B4G1PXWV</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13937.28571428571</v>
+        <v>4589</v>
       </c>
       <c r="E19" t="n">
-        <v>58.82142857142857</v>
+        <v>15</v>
       </c>
       <c r="F19" t="n">
-        <v>546.3710714285714</v>
+        <v>129.1217857142857</v>
       </c>
       <c r="G19" t="n">
-        <v>3186.528928571428</v>
+        <v>114.9817857142857</v>
       </c>
       <c r="H19" t="n">
-        <v>1.428571428571429</v>
+        <v>0</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -12420,23 +12420,23 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>B0B4K87PR4</t>
+          <t>B0B4JRQP22</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13937.28571428571</v>
+        <v>4589</v>
       </c>
       <c r="E20" t="n">
-        <v>58.82142857142857</v>
+        <v>15</v>
       </c>
       <c r="F20" t="n">
-        <v>546.3710714285714</v>
+        <v>129.1217857142857</v>
       </c>
       <c r="G20" t="n">
-        <v>3186.528928571428</v>
+        <v>114.9817857142857</v>
       </c>
       <c r="H20" t="n">
-        <v>1.428571428571429</v>
+        <v>0</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -12453,23 +12453,23 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>B0B4KC7VBM</t>
+          <t>B0B4K87PR4</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13937.28571428571</v>
+        <v>34005</v>
       </c>
       <c r="E21" t="n">
-        <v>58.82142857142857</v>
+        <v>108</v>
       </c>
       <c r="F21" t="n">
-        <v>546.3710714285714</v>
+        <v>638.3822322487828</v>
       </c>
       <c r="G21" t="n">
-        <v>3186.528928571428</v>
+        <v>4522.980582867494</v>
       </c>
       <c r="H21" t="n">
-        <v>1.428571428571429</v>
+        <v>3</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -12486,23 +12486,23 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>B0BLJVJ2GN</t>
+          <t>B0B4KC7VBM</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13937.28571428571</v>
+        <v>21500</v>
       </c>
       <c r="E22" t="n">
-        <v>58.82142857142857</v>
+        <v>68</v>
       </c>
       <c r="F22" t="n">
-        <v>546.3710714285714</v>
+        <v>421.8934221912274</v>
       </c>
       <c r="G22" t="n">
-        <v>3186.528928571428</v>
+        <v>2649.121301580878</v>
       </c>
       <c r="H22" t="n">
-        <v>1.428571428571429</v>
+        <v>2</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -12519,23 +12519,23 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>B0BLK8DNPD</t>
+          <t>B0BLJVJ2GN</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13937.28571428571</v>
+        <v>7925</v>
       </c>
       <c r="E23" t="n">
-        <v>58.82142857142857</v>
+        <v>63</v>
       </c>
       <c r="F23" t="n">
-        <v>546.3710714285714</v>
+        <v>922.5685408026022</v>
       </c>
       <c r="G23" t="n">
-        <v>3186.528928571428</v>
+        <v>3707.725927226986</v>
       </c>
       <c r="H23" t="n">
-        <v>1.428571428571429</v>
+        <v>3</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -12552,23 +12552,23 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>B0BPLZ5CGV</t>
+          <t>B0BLK8DNPD</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13937.28571428571</v>
+        <v>4589</v>
       </c>
       <c r="E24" t="n">
-        <v>58.82142857142857</v>
+        <v>15</v>
       </c>
       <c r="F24" t="n">
-        <v>546.3710714285714</v>
+        <v>129.1217857142857</v>
       </c>
       <c r="G24" t="n">
-        <v>3186.528928571428</v>
+        <v>114.9817857142857</v>
       </c>
       <c r="H24" t="n">
-        <v>1.428571428571429</v>
+        <v>0</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -12585,23 +12585,23 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>B0C4YTNJG7</t>
+          <t>B0BPLWW72Y</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13937.28571428571</v>
+        <v>24569</v>
       </c>
       <c r="E25" t="n">
-        <v>58.82142857142857</v>
+        <v>78</v>
       </c>
       <c r="F25" t="n">
-        <v>546.3710714285714</v>
+        <v>425.3379169885611</v>
       </c>
       <c r="G25" t="n">
-        <v>3186.528928571428</v>
+        <v>3681.591686980199</v>
       </c>
       <c r="H25" t="n">
-        <v>1.428571428571429</v>
+        <v>2</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -12618,23 +12618,23 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>B0C539RBGL</t>
+          <t>B0BPLZ5CGV</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13937.28571428571</v>
+        <v>114539</v>
       </c>
       <c r="E26" t="n">
-        <v>58.82142857142857</v>
+        <v>592</v>
       </c>
       <c r="F26" t="n">
-        <v>546.3710714285714</v>
+        <v>5075.260164957484</v>
       </c>
       <c r="G26" t="n">
-        <v>3186.528928571428</v>
+        <v>44414.65586747553</v>
       </c>
       <c r="H26" t="n">
-        <v>1.428571428571429</v>
+        <v>14</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -12651,23 +12651,23 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>B0CF5R3V95</t>
+          <t>B0C4YTNJG7</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13937.28571428571</v>
+        <v>4589</v>
       </c>
       <c r="E27" t="n">
-        <v>58.82142857142857</v>
+        <v>15</v>
       </c>
       <c r="F27" t="n">
-        <v>546.3710714285714</v>
+        <v>129.1217857142857</v>
       </c>
       <c r="G27" t="n">
-        <v>3186.528928571428</v>
+        <v>114.9817857142857</v>
       </c>
       <c r="H27" t="n">
-        <v>1.428571428571429</v>
+        <v>0</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -12684,23 +12684,23 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>B0CF5RRTDJ</t>
+          <t>B0C539RBGL</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13937.28571428571</v>
+        <v>4589</v>
       </c>
       <c r="E28" t="n">
-        <v>58.82142857142857</v>
+        <v>15</v>
       </c>
       <c r="F28" t="n">
-        <v>546.3710714285714</v>
+        <v>129.1217857142857</v>
       </c>
       <c r="G28" t="n">
-        <v>3186.528928571428</v>
+        <v>114.9817857142857</v>
       </c>
       <c r="H28" t="n">
-        <v>1.428571428571429</v>
+        <v>0</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -12717,23 +12717,23 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>B0CF5TCQKL</t>
+          <t>B0CF5R3V95</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13937.28571428571</v>
+        <v>4589</v>
       </c>
       <c r="E29" t="n">
-        <v>58.82142857142857</v>
+        <v>15</v>
       </c>
       <c r="F29" t="n">
-        <v>546.3710714285714</v>
+        <v>129.1217857142857</v>
       </c>
       <c r="G29" t="n">
-        <v>3186.528928571428</v>
+        <v>114.9817857142857</v>
       </c>
       <c r="H29" t="n">
-        <v>1.428571428571429</v>
+        <v>0</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -12750,23 +12750,23 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>B0CH4RT4P8</t>
+          <t>B0CF5RRTDJ</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13937.28571428571</v>
+        <v>4589</v>
       </c>
       <c r="E30" t="n">
-        <v>58.82142857142857</v>
+        <v>15</v>
       </c>
       <c r="F30" t="n">
-        <v>546.3710714285714</v>
+        <v>129.1217857142857</v>
       </c>
       <c r="G30" t="n">
-        <v>3186.528928571428</v>
+        <v>114.9817857142857</v>
       </c>
       <c r="H30" t="n">
-        <v>1.428571428571429</v>
+        <v>0</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -12783,23 +12783,23 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>B0CKHVHVQ1</t>
+          <t>B0CF5TCQKL</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13937.28571428571</v>
+        <v>15396</v>
       </c>
       <c r="E31" t="n">
-        <v>58.82142857142857</v>
+        <v>171</v>
       </c>
       <c r="F31" t="n">
-        <v>546.3710714285714</v>
+        <v>2699.494403953559</v>
       </c>
       <c r="G31" t="n">
-        <v>3186.528928571428</v>
+        <v>11753.68483221665</v>
       </c>
       <c r="H31" t="n">
-        <v>1.428571428571429</v>
+        <v>9</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -12816,23 +12816,23 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>B0CM6NTWBP</t>
+          <t>B0CH4RT4P8</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13937.28571428571</v>
+        <v>4589</v>
       </c>
       <c r="E32" t="n">
-        <v>58.82142857142857</v>
+        <v>15</v>
       </c>
       <c r="F32" t="n">
-        <v>546.3710714285714</v>
+        <v>129.1217857142857</v>
       </c>
       <c r="G32" t="n">
-        <v>3186.528928571428</v>
+        <v>114.9817857142857</v>
       </c>
       <c r="H32" t="n">
-        <v>1.428571428571429</v>
+        <v>0</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -12849,23 +12849,23 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>B0D3M1B4Z8</t>
+          <t>B0CKHVHVQ1</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13937.28571428571</v>
+        <v>4589</v>
       </c>
       <c r="E33" t="n">
-        <v>58.82142857142857</v>
+        <v>15</v>
       </c>
       <c r="F33" t="n">
-        <v>546.3710714285714</v>
+        <v>129.1217857142857</v>
       </c>
       <c r="G33" t="n">
-        <v>3186.528928571428</v>
+        <v>114.9817857142857</v>
       </c>
       <c r="H33" t="n">
-        <v>1.428571428571429</v>
+        <v>0</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -12882,23 +12882,23 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>B0DFMLS8JG</t>
+          <t>B0CM6NTWBP</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13937.28571428571</v>
+        <v>29724</v>
       </c>
       <c r="E34" t="n">
-        <v>58.82142857142857</v>
+        <v>67</v>
       </c>
       <c r="F34" t="n">
-        <v>546.3710714285714</v>
+        <v>423.5186433682485</v>
       </c>
       <c r="G34" t="n">
-        <v>3186.528928571428</v>
+        <v>2708.201785714286</v>
       </c>
       <c r="H34" t="n">
-        <v>1.428571428571429</v>
+        <v>1</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -12915,23 +12915,23 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>B0DFMMTWLY</t>
+          <t>B0D3M1B4Z8</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13937.28571428571</v>
+        <v>4589</v>
       </c>
       <c r="E35" t="n">
-        <v>58.82142857142857</v>
+        <v>15</v>
       </c>
       <c r="F35" t="n">
-        <v>546.3710714285714</v>
+        <v>129.1217857142857</v>
       </c>
       <c r="G35" t="n">
-        <v>3186.528928571428</v>
+        <v>114.9817857142857</v>
       </c>
       <c r="H35" t="n">
-        <v>1.428571428571429</v>
+        <v>0</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -12948,23 +12948,23 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>B0DFMNGFTD</t>
+          <t>B0DFMLS8JG</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13937.28571428571</v>
+        <v>4589</v>
       </c>
       <c r="E36" t="n">
-        <v>58.82142857142857</v>
+        <v>15</v>
       </c>
       <c r="F36" t="n">
-        <v>546.3710714285714</v>
+        <v>129.1217857142857</v>
       </c>
       <c r="G36" t="n">
-        <v>3186.528928571428</v>
+        <v>114.9817857142857</v>
       </c>
       <c r="H36" t="n">
-        <v>1.428571428571429</v>
+        <v>0</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -12981,23 +12981,23 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>B0DT6T6N6B</t>
+          <t>B0DFMMTWLY</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13937.28571428571</v>
+        <v>4589</v>
       </c>
       <c r="E37" t="n">
-        <v>58.82142857142857</v>
+        <v>15</v>
       </c>
       <c r="F37" t="n">
-        <v>546.3710714285714</v>
+        <v>129.1217857142857</v>
       </c>
       <c r="G37" t="n">
-        <v>3186.528928571428</v>
+        <v>114.9817857142857</v>
       </c>
       <c r="H37" t="n">
-        <v>1.428571428571429</v>
+        <v>0</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -13014,23 +13014,23 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>B0FF9R3GKK</t>
+          <t>B0DFMNGFTD</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13937.28571428571</v>
+        <v>4589</v>
       </c>
       <c r="E38" t="n">
-        <v>58.82142857142857</v>
+        <v>15</v>
       </c>
       <c r="F38" t="n">
-        <v>546.3710714285714</v>
+        <v>129.1217857142857</v>
       </c>
       <c r="G38" t="n">
-        <v>3186.528928571428</v>
+        <v>114.9817857142857</v>
       </c>
       <c r="H38" t="n">
-        <v>1.428571428571429</v>
+        <v>0</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -13047,23 +13047,23 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>B0G2C2RCXN</t>
+          <t>B0DT6T6N6B</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>13937.28571428571</v>
+        <v>5637</v>
       </c>
       <c r="E39" t="n">
-        <v>58.82142857142857</v>
+        <v>30</v>
       </c>
       <c r="F39" t="n">
-        <v>546.3710714285714</v>
+        <v>378.3924123866961</v>
       </c>
       <c r="G39" t="n">
-        <v>3186.528928571428</v>
+        <v>1243.684597699217</v>
       </c>
       <c r="H39" t="n">
-        <v>1.428571428571429</v>
+        <v>1</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -13080,23 +13080,23 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>B0G3Q517Y2</t>
+          <t>B0FF9R3GKK</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>13937.28571428571</v>
+        <v>4589</v>
       </c>
       <c r="E40" t="n">
-        <v>58.82142857142857</v>
+        <v>15</v>
       </c>
       <c r="F40" t="n">
-        <v>546.3710714285714</v>
+        <v>129.1217857142857</v>
       </c>
       <c r="G40" t="n">
-        <v>3186.528928571428</v>
+        <v>114.9817857142857</v>
       </c>
       <c r="H40" t="n">
-        <v>1.428571428571429</v>
+        <v>0</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -13113,23 +13113,23 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>B0G3Q59X8C</t>
+          <t>B0FJ2DT13L</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>13937.28571428571</v>
+        <v>9598</v>
       </c>
       <c r="E41" t="n">
-        <v>58.82142857142857</v>
+        <v>50</v>
       </c>
       <c r="F41" t="n">
-        <v>546.3710714285714</v>
+        <v>431.7816207568009</v>
       </c>
       <c r="G41" t="n">
-        <v>3186.528928571428</v>
+        <v>3867.215918238751</v>
       </c>
       <c r="H41" t="n">
-        <v>1.428571428571429</v>
+        <v>1</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -13146,25 +13146,157 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
+          <t>B0FLYJFC22</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>19295</v>
+      </c>
+      <c r="E42" t="n">
+        <v>40</v>
+      </c>
+      <c r="F42" t="n">
+        <v>225.9931423460372</v>
+      </c>
+      <c r="G42" t="n">
+        <v>1990.68</v>
+      </c>
+      <c r="H42" t="n">
+        <v>1</v>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr"/>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Audio Array-Multiple Ad Group-SB-PT</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>B0G2C2RCXN</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>4589</v>
+      </c>
+      <c r="E43" t="n">
+        <v>15</v>
+      </c>
+      <c r="F43" t="n">
+        <v>129.1217857142857</v>
+      </c>
+      <c r="G43" t="n">
+        <v>114.9817857142857</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr"/>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Audio Array-Multiple Ad Group-SB-PT</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>B0G3Q517Y2</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>4589</v>
+      </c>
+      <c r="E44" t="n">
+        <v>15</v>
+      </c>
+      <c r="F44" t="n">
+        <v>129.1217857142857</v>
+      </c>
+      <c r="G44" t="n">
+        <v>114.9817857142857</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr"/>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Audio Array-Multiple Ad Group-SB-PT</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>B0G3Q59X8C</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>4589</v>
+      </c>
+      <c r="E45" t="n">
+        <v>15</v>
+      </c>
+      <c r="F45" t="n">
+        <v>129.1217857142857</v>
+      </c>
+      <c r="G45" t="n">
+        <v>114.9817857142857</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr"/>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Audio Array-Multiple Ad Group-SB-PT</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
           <t>B0G4DNF8RZ</t>
         </is>
       </c>
-      <c r="D42" t="n">
-        <v>13937.28571428571</v>
-      </c>
-      <c r="E42" t="n">
-        <v>58.82142857142857</v>
-      </c>
-      <c r="F42" t="n">
-        <v>546.3710714285714</v>
-      </c>
-      <c r="G42" t="n">
-        <v>3186.528928571428</v>
-      </c>
-      <c r="H42" t="n">
-        <v>1.428571428571429</v>
-      </c>
-      <c r="I42" t="inlineStr">
+      <c r="D46" t="n">
+        <v>4589</v>
+      </c>
+      <c r="E46" t="n">
+        <v>15</v>
+      </c>
+      <c r="F46" t="n">
+        <v>129.1217857142857</v>
+      </c>
+      <c r="G46" t="n">
+        <v>114.9817857142857</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" t="inlineStr">
         <is>
           <t>Audio Array</t>
         </is>

--- a/data/ams_weekly_data/Audio_Array/ads_report_week18.xlsx
+++ b/data/ams_weekly_data/Audio_Array/ads_report_week18.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="SP" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="SD" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="SB" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SP" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SD" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SB" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
